--- a/diseases/d033/1990-1994.xlsx
+++ b/diseases/d033/1990-1994.xlsx
@@ -19909,7 +19909,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -21728,7 +21728,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22528,7 +22528,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23328,7 +23328,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -23728,7 +23728,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24528,7 +24528,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -24928,7 +24928,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31286,7 +31286,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -31686,7 +31686,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -32486,7 +32486,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -32886,7 +32886,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -33286,7 +33286,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -34086,7 +34086,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -34486,7 +34486,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -34886,7 +34886,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -35286,7 +35286,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">

--- a/diseases/d033/1990-1994.xlsx
+++ b/diseases/d033/1990-1994.xlsx
@@ -19909,7 +19909,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -21728,7 +21728,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22528,7 +22528,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23328,7 +23328,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -23728,7 +23728,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24528,7 +24528,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -24928,7 +24928,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -31286,7 +31286,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -31686,7 +31686,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -32486,7 +32486,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -32886,7 +32886,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -33286,7 +33286,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -34086,7 +34086,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -34486,7 +34486,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -34886,7 +34886,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -35286,7 +35286,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
